--- a/bmi_records.xlsx
+++ b/bmi_records.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dushyant/BMI-calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B18FF666-7801-0149-AAA9-BABF68F8DA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433CC633-E20B-B147-9191-4A3274F7CFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="580" windowWidth="25440" windowHeight="14580" xr2:uid="{098C6C4D-51FB-F34B-B6A7-3A75B3383372}"/>
   </bookViews>
@@ -35,15 +35,42 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Height(cms)</t>
+  </si>
+  <si>
+    <t>Weight(kgs)</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +81,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,12 +89,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +445,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FEE9870-B882-5946-A7A7-6D5CBDB2ACFC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>